--- a/research/traditional_assets/database/data/nigeria/nigeria_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_paper_forest_products.xlsx
@@ -587,23 +587,26 @@
           <t>Paper/Forest Products</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.121</v>
+      </c>
       <c r="G2">
-        <v>-0.2580645161290323</v>
+        <v>0.9084967320261439</v>
       </c>
       <c r="H2">
-        <v>-0.2580645161290323</v>
+        <v>0.9084967320261439</v>
       </c>
       <c r="I2">
-        <v>-2.943548387096774</v>
+        <v>0.5163398692810458</v>
       </c>
       <c r="J2">
-        <v>-2.943548387096774</v>
+        <v>0.5098039215686275</v>
       </c>
       <c r="K2">
-        <v>-0.12</v>
+        <v>0.074</v>
       </c>
       <c r="L2">
-        <v>-0.9677419354838709</v>
+        <v>0.4836601307189543</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,52 +624,52 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="V2">
-        <v>0.01470588235294118</v>
+        <v>0.0025</v>
       </c>
       <c r="W2">
-        <v>0.1655172413793103</v>
+        <v>-0.09169764560099132</v>
       </c>
       <c r="X2">
-        <v>0.2897165113090855</v>
+        <v>0.1636256288056476</v>
       </c>
       <c r="Y2">
-        <v>-0.1241992699297752</v>
+        <v>-0.2553232744066389</v>
       </c>
       <c r="AB2">
-        <v>0.174791145326716</v>
+        <v>0.1479820235329705</v>
       </c>
       <c r="AD2">
-        <v>0.636</v>
+        <v>0.352</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.636</v>
+        <v>0.352</v>
       </c>
       <c r="AG2">
-        <v>0.629</v>
+        <v>0.349</v>
       </c>
       <c r="AH2">
-        <v>0.5719424460431655</v>
+        <v>0.2268041237113402</v>
       </c>
       <c r="AI2">
-        <v>-3.719298245614034</v>
+        <v>0.3537688442211055</v>
       </c>
       <c r="AJ2">
-        <v>0.5692307692307692</v>
+        <v>0.2253066494512589</v>
       </c>
       <c r="AK2">
-        <v>-3.533707865168538</v>
+        <v>0.3518145161290323</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -675,10 +678,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>-1.904191616766467</v>
+        <v>3.229357798165137</v>
       </c>
       <c r="AP2">
-        <v>-1.883233532934132</v>
+        <v>3.201834862385321</v>
       </c>
     </row>
     <row r="3">
@@ -697,23 +700,26 @@
           <t>Paper/Forest Products</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.121</v>
+      </c>
       <c r="G3">
-        <v>-0.2580645161290323</v>
+        <v>0.9084967320261439</v>
       </c>
       <c r="H3">
-        <v>-0.2580645161290323</v>
+        <v>0.9084967320261439</v>
       </c>
       <c r="I3">
-        <v>-2.943548387096774</v>
+        <v>0.5163398692810458</v>
       </c>
       <c r="J3">
-        <v>-2.943548387096774</v>
+        <v>0.5098039215686275</v>
       </c>
       <c r="K3">
-        <v>-0.12</v>
+        <v>0.074</v>
       </c>
       <c r="L3">
-        <v>-0.9677419354838709</v>
+        <v>0.4836601307189543</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,7 +728,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -731,52 +737,52 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="V3">
-        <v>0.01470588235294118</v>
+        <v>0.0025</v>
       </c>
       <c r="W3">
-        <v>0.1655172413793103</v>
+        <v>-0.09169764560099132</v>
       </c>
       <c r="X3">
-        <v>0.2897165113090855</v>
+        <v>0.1636256288056476</v>
       </c>
       <c r="Y3">
-        <v>-0.1241992699297752</v>
+        <v>-0.2553232744066389</v>
       </c>
       <c r="AB3">
-        <v>0.174791145326716</v>
+        <v>0.1479820235329705</v>
       </c>
       <c r="AD3">
-        <v>0.636</v>
+        <v>0.352</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.636</v>
+        <v>0.352</v>
       </c>
       <c r="AG3">
-        <v>0.629</v>
+        <v>0.349</v>
       </c>
       <c r="AH3">
-        <v>0.5719424460431655</v>
+        <v>0.2268041237113402</v>
       </c>
       <c r="AI3">
-        <v>-3.719298245614034</v>
+        <v>0.3537688442211055</v>
       </c>
       <c r="AJ3">
-        <v>0.5692307692307692</v>
+        <v>0.2253066494512589</v>
       </c>
       <c r="AK3">
-        <v>-3.533707865168538</v>
+        <v>0.3518145161290323</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -785,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-1.904191616766467</v>
+        <v>3.229357798165137</v>
       </c>
       <c r="AP3">
-        <v>-1.883233532934132</v>
+        <v>3.201834862385321</v>
       </c>
     </row>
   </sheetData>
